--- a/backend/data/onboarding/source/180-day-checklist.xlsx
+++ b/backend/data/onboarding/source/180-day-checklist.xlsx
@@ -58,7 +58,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -175,6 +175,25 @@
       <b val="1"/>
       <color rgb="FF203864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF0563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF0563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="28">
@@ -321,7 +340,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -344,12 +363,56 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -629,6 +692,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -842,6 +919,176 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>NRO links</author>
+  </authors>
+  <commentList>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000880525-newk-s-website-information-form-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880546-msi-catering-platform-questionnaire-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000880548-logging-to-accounts-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880593-low-voltage-vendors-and-review-plans-with-pos-vendor-for-new-restaur</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Recovered from the app catalog.
+Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000892720-nro-checklist-toast-point-of-sale-and-credit-card-processing
+Previous cell text:
+NRO Checklist - Toast Point of Sale and Credit Card Processing : Newk's - Knowledgebase</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://fscticket.freshdesk.com/support/tickets/new</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Recovered from the app catalog.
+Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881312-nro-high-speed-internet-provider</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000892718-nro-checklist-paytronix-gift-card-participation-form</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880674-olo-and-olo-pay-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000891349-nro-checklist-sign-up-with-opus-training-elearning-platform</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000866209-american-express-setup-process-for-new-restaurant-opening-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880736-plug-and-pay-for-new-restaurant-openings-and-catering-payments-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880749-dtiq-or-envysion-cctv-cameras-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881313-nro-burglar-and-fire-alarm-sourcing</t>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881312-nro-high-speed-internet-provider</t>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000880748-nro-checklist-choose-a-voice-telephone-provider-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F33" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000881276-nro-checklist-directv-music-choice-for-new-restaurant-openings-nro-</t>
+      </text>
+    </comment>
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881323-nro-prep-n-print</t>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000891349-nro-checklist-sign-up-with-opus-training-elearning-platform</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881321-nro-newksgear-com</t>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881322-nro-newk-s-marketing-toolkit-access</t>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881316-nro-ezcater-catering-sales-marketplace</t>
+      </text>
+    </comment>
+    <comment ref="F39" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881319-nro-establishing-accounts-with-3rd-party-delivery-marketplaces</t>
+      </text>
+    </comment>
+    <comment ref="F40" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881320-nro-punchh-loyalty-promotion-and-discounting-platform</t>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/en/support/solutions/articles/5000881317-nro-triple-impact-catering-call-center-services</t>
+      </text>
+    </comment>
+    <comment ref="F42" authorId="0" shapeId="0">
+      <text>
+        <t>Full link:
+https://newksit.freshdesk.com/support/solutions/articles/5000892719-nro-checklist-verify-accuracy-of-local-listings-via-yext-platform</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1419,19 +1666,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -1448,17 +1695,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -1474,19 +1721,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -1503,17 +1750,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -1590,7 +1837,7 @@
           <t>Accounting Department</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="104" t="inlineStr">
         <is>
           <t>accounting@newks.com</t>
         </is>
@@ -1626,7 +1873,7 @@
           <t>Accounting Department</t>
         </is>
       </c>
-      <c r="G9" s="91" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>accounting@newks.com</t>
         </is>
@@ -1662,7 +1909,7 @@
           <t>Accounting Department</t>
         </is>
       </c>
-      <c r="G10" s="87" t="inlineStr">
+      <c r="G10" s="104" t="inlineStr">
         <is>
           <t>accounting@newks.com</t>
         </is>
@@ -1710,6 +1957,11 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -1755,19 +2007,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -1784,17 +2036,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -1810,19 +2062,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -1839,17 +2091,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -1946,7 +2198,7 @@
         </is>
       </c>
       <c r="F9" s="90" t="n"/>
-      <c r="G9" s="91" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>salesteam@newks.com</t>
         </is>
@@ -1994,6 +2246,9 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -2065,8 +2320,8 @@
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
-      <c r="E3" s="79" t="n"/>
+      <c r="D3" s="100" t="n"/>
+      <c r="E3" s="101" t="n"/>
       <c r="F3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -2098,8 +2353,8 @@
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
-      <c r="E4" s="81" t="n"/>
+      <c r="D4" s="100" t="n"/>
+      <c r="E4" s="101" t="n"/>
       <c r="F4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -2132,8 +2387,8 @@
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
-      <c r="E5" s="79" t="n"/>
+      <c r="D5" s="100" t="n"/>
+      <c r="E5" s="101" t="n"/>
       <c r="F5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -2165,8 +2420,8 @@
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
-      <c r="E6" s="81" t="n"/>
+      <c r="D6" s="100" t="n"/>
+      <c r="E6" s="101" t="n"/>
       <c r="F6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -2263,9 +2518,9 @@
           <t>180 Days from Opening</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/support/solutions/articles/5000880525-newk-s-website-information-form-for-new-restaurant-openings-nro-</t>
+      <c r="F9" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -2302,9 +2557,9 @@
           <t>180 Days from Opening</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880546-msi-catering-platform-questionnaire-for-new-restaurant-openings-nro-</t>
+      <c r="F10" s="103" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2369,9 +2624,9 @@
           <t>180 Days from Opening</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/support/solutions/articles/5000880548-logging-to-accounts-for-new-restaurant-openings-nro-</t>
+      <c r="F11" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -2436,9 +2691,9 @@
           <t>Construction Phase</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880593-low-voltage-vendors-and-review-plans-with-pos-vendor-for-new-restaur</t>
+      <c r="F12" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -2496,9 +2751,9 @@
           <t>Minimum 8 Weeks Prior</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>NRO Checklist - Toast Point of Sale and Credit Card Processing : Newk's - Knowledgebase</t>
+      <c r="F15" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -2535,9 +2790,9 @@
           <t>Contact Early</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>https://fscticket.freshdesk.com/support/tickets/new</t>
+      <c r="F16" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -2574,7 +2829,11 @@
           <t>Contact Early</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n"/>
+      <c r="F17" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>☐</t>
@@ -2644,9 +2903,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/support/solutions/articles/5000892718-nro-checklist-paytronix-gift-card-participation-form</t>
+      <c r="F19" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -2683,9 +2942,9 @@
           <t>50 Days Prior to Opening</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880674-olo-and-olo-pay-for-new-restaurant-openings-nro-</t>
+      <c r="F20" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2722,9 +2981,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000891349-nro-checklist-sign-up-with-opus-training-elearning-platform</t>
+      <c r="F21" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -2800,9 +3059,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000866209-american-express-setup-process-for-new-restaurant-opening-nro-</t>
+      <c r="F23" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -2839,9 +3098,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880736-plug-and-pay-for-new-restaurant-openings-and-catering-payments-nro-</t>
+      <c r="F24" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -2878,9 +3137,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880749-dtiq-or-envysion-cctv-cameras-for-new-restaurant-openings-nro-</t>
+      <c r="F25" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2938,9 +3197,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881313-nro-burglar-and-fire-alarm-sourcing</t>
+      <c r="F28" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2976,9 +3235,9 @@
           <t>Contact ISS First</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881312-nro-high-speed-internet-provider</t>
+      <c r="F29" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -3013,9 +3272,9 @@
           <t>Contact ISS First</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000880748-nro-checklist-choose-a-voice-telephone-provider-nro-</t>
+      <c r="F30" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -3067,9 +3326,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/support/solutions/articles/5000881276-nro-checklist-directv-music-choice-for-new-restaurant-openings-nro-</t>
+      <c r="F33" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -3104,9 +3363,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881323-nro-prep-n-print</t>
+      <c r="F34" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3141,9 +3400,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000891349-nro-checklist-sign-up-with-opus-training-elearning-platform</t>
+      <c r="F35" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -3178,9 +3437,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881321-nro-newksgear-com</t>
+      <c r="F36" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -3215,9 +3474,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881322-nro-newk-s-marketing-toolkit-access</t>
+      <c r="F37" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -3252,9 +3511,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881316-nro-ezcater-catering-sales-marketplace</t>
+      <c r="F38" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -3289,9 +3548,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881319-nro-establishing-accounts-with-3rd-party-delivery-marketplaces</t>
+      <c r="F39" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -3326,9 +3585,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881320-nro-punchh-loyalty-promotion-and-discounting-platform</t>
+      <c r="F40" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -3363,9 +3622,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/en/support/solutions/articles/5000881317-nro-triple-impact-catering-call-center-services</t>
+      <c r="F41" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -3400,9 +3659,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>https://newksit.freshdesk.com/support/solutions/articles/5000892719-nro-checklist-verify-accuracy-of-local-listings-via-yext-platform</t>
+      <c r="F42" s="102" t="inlineStr">
+        <is>
+          <t>KB Article ↗</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -3411,6 +3670,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="39" t="inlineStr">
         <is>
@@ -3447,8 +3707,37 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3492,19 +3781,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -3521,17 +3810,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -3547,19 +3836,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -3576,17 +3865,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -3663,7 +3952,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3699,7 +3988,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G9" s="91" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3787,7 +4076,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G12" s="87" t="inlineStr">
+      <c r="G12" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3823,7 +4112,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G13" s="91" t="inlineStr">
+      <c r="G13" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3859,7 +4148,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G14" s="87" t="inlineStr">
+      <c r="G14" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3895,7 +4184,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G15" s="91" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3931,7 +4220,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G16" s="87" t="inlineStr">
+      <c r="G16" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -3967,7 +4256,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G17" s="91" t="inlineStr">
+      <c r="G17" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4147,7 +4436,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G22" s="87" t="inlineStr">
+      <c r="G22" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4183,7 +4472,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G23" s="91" t="inlineStr">
+      <c r="G23" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4219,7 +4508,7 @@
           <t>Field Marketing</t>
         </is>
       </c>
-      <c r="G24" s="87" t="inlineStr">
+      <c r="G24" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4291,7 +4580,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G26" s="87" t="inlineStr">
+      <c r="G26" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4327,7 +4616,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G27" s="91" t="inlineStr">
+      <c r="G27" s="105" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4363,7 +4652,7 @@
           <t>Marketing Department /</t>
         </is>
       </c>
-      <c r="G28" s="87" t="inlineStr">
+      <c r="G28" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -4411,6 +4700,22 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -4456,19 +4761,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -4485,17 +4790,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -4511,19 +4816,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -4540,17 +4845,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -4627,7 +4932,7 @@
           <t>Jessica Drahem</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="104" t="inlineStr">
         <is>
           <t>pdc@newks.com</t>
         </is>
@@ -4663,7 +4968,7 @@
           <t>Training (PD&amp;C)</t>
         </is>
       </c>
-      <c r="G9" s="91" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>pdc@newks.com</t>
         </is>
@@ -4699,7 +5004,7 @@
           <t>Jessica Drahem</t>
         </is>
       </c>
-      <c r="G10" s="87" t="inlineStr">
+      <c r="G10" s="104" t="inlineStr">
         <is>
           <t>pdc@newks.com</t>
         </is>
@@ -4735,7 +5040,7 @@
           <t>Jessica Drahem</t>
         </is>
       </c>
-      <c r="G11" s="91" t="inlineStr">
+      <c r="G11" s="105" t="inlineStr">
         <is>
           <t>pdc@newks.com</t>
         </is>
@@ -4867,7 +5172,7 @@
           <t>Jessica Drahem</t>
         </is>
       </c>
-      <c r="G15" s="91" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>pdc@newks.com</t>
         </is>
@@ -5011,6 +5316,13 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -5056,19 +5368,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -5085,17 +5397,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -5111,19 +5423,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -5140,17 +5452,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -5872,19 +6184,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -5901,17 +6213,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -5927,19 +6239,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -5956,17 +6268,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -6043,7 +6355,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -6199,7 +6511,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G14" s="87" t="inlineStr">
+      <c r="G14" s="104" t="inlineStr">
         <is>
           <t>Fieldmarketing@newks.com</t>
         </is>
@@ -6235,7 +6547,7 @@
           <t>Matilyn Skinner</t>
         </is>
       </c>
-      <c r="G15" s="91" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>Fieldmarketing@newks.com</t>
         </is>
@@ -6439,7 +6751,7 @@
           <t>Carmen Wilson</t>
         </is>
       </c>
-      <c r="G23" s="91" t="inlineStr">
+      <c r="G23" s="105" t="inlineStr">
         <is>
           <t>carmen.wilson@airadpromotions.com</t>
         </is>
@@ -6475,7 +6787,7 @@
           <t>ColorMark</t>
         </is>
       </c>
-      <c r="G24" s="87" t="inlineStr">
+      <c r="G24" s="104" t="inlineStr">
         <is>
           <t>fieldmarketing@newks.com</t>
         </is>
@@ -7183,6 +7495,13 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -7228,19 +7547,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -7257,17 +7576,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -7283,19 +7602,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -7312,17 +7631,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -7399,7 +7718,7 @@
           <t>Klara Smith</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="104" t="inlineStr">
         <is>
           <t>ksmith@newks.com</t>
         </is>
@@ -7447,6 +7766,9 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -7492,19 +7814,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -7521,17 +7843,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -7547,19 +7869,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -7576,17 +7898,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
@@ -7735,7 +8057,7 @@
           <t>Alyssa Ownby</t>
         </is>
       </c>
-      <c r="G10" s="87" t="inlineStr">
+      <c r="G10" s="104" t="inlineStr">
         <is>
           <t>aownby@coca-cola.com</t>
         </is>
@@ -7771,7 +8093,7 @@
           <t>Ellis Bridgers</t>
         </is>
       </c>
-      <c r="G11" s="91" t="inlineStr">
+      <c r="G11" s="105" t="inlineStr">
         <is>
           <t>Ellis.Bridgers@GAPAC.com</t>
         </is>
@@ -7908,7 +8230,7 @@
       </c>
       <c r="E15" s="90" t="n"/>
       <c r="F15" s="90" t="n"/>
-      <c r="G15" s="91" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>purchasing@newks.com</t>
         </is>
@@ -7936,7 +8258,7 @@
       </c>
       <c r="E16" s="86" t="n"/>
       <c r="F16" s="86" t="n"/>
-      <c r="G16" s="87" t="inlineStr">
+      <c r="G16" s="104" t="inlineStr">
         <is>
           <t>purchasing@newks.com</t>
         </is>
@@ -8183,7 +8505,7 @@
       </c>
       <c r="E23" s="90" t="n"/>
       <c r="F23" s="90" t="n"/>
-      <c r="G23" s="91" t="inlineStr">
+      <c r="G23" s="105" t="inlineStr">
         <is>
           <t>purchasing@newks.com</t>
         </is>
@@ -8211,7 +8533,7 @@
       </c>
       <c r="E24" s="86" t="n"/>
       <c r="F24" s="86" t="n"/>
-      <c r="G24" s="87" t="inlineStr">
+      <c r="G24" s="104" t="inlineStr">
         <is>
           <t>purchasing@newks.com</t>
         </is>
@@ -8297,6 +8619,14 @@
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -8342,19 +8672,19 @@
           <t>REST. #</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="101" t="n"/>
       <c r="C3" s="78" t="inlineStr">
         <is>
           <t>RESTAURANT NAME</t>
         </is>
       </c>
-      <c r="D3" s="79" t="n"/>
+      <c r="D3" s="101" t="n"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="F3" s="79" t="n"/>
+      <c r="F3" s="101" t="n"/>
       <c r="G3" s="78" t="inlineStr">
         <is>
           <t>TELEPHONE</t>
@@ -8371,17 +8701,17 @@
         <f>IF('NRO Info'!$C$5="","",'NRO Info'!$C$5)</f>
         <v/>
       </c>
-      <c r="B4" s="81" t="n"/>
+      <c r="B4" s="101" t="n"/>
       <c r="C4" s="80">
         <f>IF('NRO Info'!$C$6="","",'NRO Info'!$C$6)</f>
         <v/>
       </c>
-      <c r="D4" s="81" t="n"/>
+      <c r="D4" s="101" t="n"/>
       <c r="E4" s="80">
         <f>IF('NRO Info'!$C$7="","",'NRO Info'!$C$7)</f>
         <v/>
       </c>
-      <c r="F4" s="81" t="n"/>
+      <c r="F4" s="101" t="n"/>
       <c r="G4" s="80">
         <f>IF('NRO Info'!$C$8="","",'NRO Info'!$C$8)</f>
         <v/>
@@ -8397,19 +8727,19 @@
           <t>GROUND BREAKING</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
+      <c r="B5" s="101" t="n"/>
       <c r="C5" s="78" t="inlineStr">
         <is>
           <t>BUILD TIME</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
+      <c r="D5" s="101" t="n"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>TURN OVER</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
+      <c r="F5" s="101" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>HIRING DATE</t>
@@ -8426,17 +8756,17 @@
         <f>IF('NRO Info'!$C$9="","",'NRO Info'!$C$9)</f>
         <v/>
       </c>
-      <c r="B6" s="81" t="n"/>
+      <c r="B6" s="101" t="n"/>
       <c r="C6" s="80">
         <f>IF('NRO Info'!$C$10="","",'NRO Info'!$C$10)</f>
         <v/>
       </c>
-      <c r="D6" s="81" t="n"/>
+      <c r="D6" s="101" t="n"/>
       <c r="E6" s="80">
         <f>IF('NRO Info'!$C$11="","",'NRO Info'!$C$11)</f>
         <v/>
       </c>
-      <c r="F6" s="81" t="n"/>
+      <c r="F6" s="101" t="n"/>
       <c r="G6" s="80">
         <f>IF('NRO Info'!$C$13="","",'NRO Info'!$C$13)</f>
         <v/>
